--- a/Model_data/OffTarget_amplicon_check/primers_offTarget_test.xlsx
+++ b/Model_data/OffTarget_amplicon_check/primers_offTarget_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haoyu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47245151-AE85-419F-9CE1-18D04EC22F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CEA531-8C1F-4385-86A9-D34A8D70B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7788" yWindow="-108" windowWidth="23040" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="1140" windowWidth="23040" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="134">
   <si>
     <t>seq_type</t>
   </si>
@@ -43,21 +43,12 @@
     <t>v_region</t>
   </si>
   <si>
-    <t>27F_338R</t>
-  </si>
-  <si>
     <t>AGAGTTTGATCCTGGCTCAG</t>
   </si>
   <si>
-    <t>311bp</t>
-  </si>
-  <si>
     <t>PE250</t>
   </si>
   <si>
-    <t>v1v2</t>
-  </si>
-  <si>
     <t>27F_533R</t>
   </si>
   <si>
@@ -115,48 +106,9 @@
     <t>v4v4</t>
   </si>
   <si>
-    <t>787F_1073R</t>
-  </si>
-  <si>
-    <t>ATTAGATACCCYGGTAGTCC</t>
-  </si>
-  <si>
-    <t>ACGAGCTGACGACARCATG</t>
-  </si>
-  <si>
-    <t>286bp</t>
-  </si>
-  <si>
-    <t>v5v6</t>
-  </si>
-  <si>
-    <t>799F_1193R</t>
-  </si>
-  <si>
-    <t>AACMGGATAGATACCCKG</t>
-  </si>
-  <si>
-    <t>ACGTCATCCCCACCTTCC</t>
-  </si>
-  <si>
-    <t>394bp</t>
-  </si>
-  <si>
     <t>v5v7</t>
   </si>
   <si>
-    <t>969F_1406R</t>
-  </si>
-  <si>
-    <t>ACGCGHNRAACCTTACC</t>
-  </si>
-  <si>
-    <t>ACGGGCRGTGWGTRCAA</t>
-  </si>
-  <si>
-    <t>437bp</t>
-  </si>
-  <si>
     <t>v6v8</t>
   </si>
   <si>
@@ -194,18 +146,6 @@
   </si>
   <si>
     <t>492bp</t>
-  </si>
-  <si>
-    <t>939F_1378R</t>
-  </si>
-  <si>
-    <t>GAATTGACGGGGGCCCGCACAAG</t>
-  </si>
-  <si>
-    <t>CGGTGTGTACAAGGCCCGGGAACG</t>
-  </si>
-  <si>
-    <t>439bp</t>
   </si>
   <si>
     <t>bacterial 16S rRNA</t>
@@ -224,10 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TGCTGCCTCCCGTAGGAGT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GCTGCCTCCCGTAGGAGT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -245,10 +181,6 @@
   </si>
   <si>
     <t>v1v3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GTGYCAGCMGCCGCGGTAA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -887,12 +819,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.69921875" customWidth="1"/>
     <col min="4" max="4" width="26.8984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -923,768 +855,653 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
+      <c r="G11" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>16</v>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
+      <c r="G13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
+        <v>110</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" t="s">
-        <v>71</v>
+      <c r="C15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
+        <v>112</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>151</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>155</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1692,7 +1509,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 B3:G5 B2:C2 B7:G13 B6 E6:G6 E2:G2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 B3:G5 B7:G8 B6 E6:G6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Model_data/OffTarget_amplicon_check/primers_offTarget_test.xlsx
+++ b/Model_data/OffTarget_amplicon_check/primers_offTarget_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haoyu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CEA531-8C1F-4385-86A9-D34A8D70B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A85B61-12B8-4F3B-88E0-84E793D360E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1140" windowWidth="23040" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="108">
   <si>
     <t>seq_type</t>
   </si>
@@ -152,10 +152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GTGYCAGCMGCCGCGGTA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GGACTACHVGGGTWTCTAAT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,9 +188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bacterial 17S rRNA</t>
-  </si>
-  <si>
     <t>Post</t>
   </si>
   <si>
@@ -357,82 +350,12 @@
     <t>Ty</t>
   </si>
   <si>
-    <t>bacterial 18S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 19S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 20S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 21S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 22S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 23S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 24S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 25S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 26S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 27S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 28S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 29S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 30S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 31S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 32S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 33S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 34S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 35S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 36S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 37S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 38S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 39S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 40S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 41S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 42S rRNA</t>
-  </si>
-  <si>
-    <t>bacterial 43S rRNA</t>
+    <t>GTGYCAGCMGCCGCGGT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v4v4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -822,7 +745,7 @@
   <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.3984375" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.69921875" customWidth="1"/>
     <col min="4" max="4" width="26.8984375" bestFit="1" customWidth="1"/>
@@ -953,10 +876,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -1019,16 +942,16 @@
         <v>42</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1036,81 +959,81 @@
         <v>42</v>
       </c>
       <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
@@ -1118,16 +1041,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>18</v>
@@ -1135,16 +1058,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>18</v>
@@ -1152,16 +1075,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>18</v>
@@ -1169,16 +1092,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>18</v>
@@ -1186,16 +1109,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>18</v>
@@ -1203,84 +1126,84 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>18</v>
@@ -1288,16 +1211,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>18</v>
@@ -1305,16 +1228,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>18</v>
@@ -1322,16 +1245,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>18</v>
@@ -1339,16 +1262,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>18</v>
@@ -1356,33 +1279,33 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>23</v>
@@ -1390,16 +1313,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>23</v>
@@ -1407,33 +1330,33 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>18</v>
@@ -1441,16 +1364,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>18</v>
@@ -1458,16 +1381,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>18</v>
@@ -1475,16 +1398,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>18</v>
@@ -1492,16 +1415,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
